--- a/fsh-datatypes/ig/cm-v3-administrative-gender.xlsx
+++ b/fsh-datatypes/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:25:56+00:00</t>
+    <t>2026-04-08T14:49:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fsh-datatypes/ig/cm-v3-administrative-gender.xlsx
+++ b/fsh-datatypes/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:49:56+00:00</t>
+    <t>2026-04-08T15:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fsh-datatypes/ig/cm-v3-administrative-gender.xlsx
+++ b/fsh-datatypes/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T15:17:01+00:00</t>
+    <t>2026-04-08T15:16:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fsh-datatypes/ig/cm-v3-administrative-gender.xlsx
+++ b/fsh-datatypes/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T15:16:22+00:00</t>
+    <t>2026-04-08T15:36:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fsh-datatypes/ig/cm-v3-administrative-gender.xlsx
+++ b/fsh-datatypes/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T15:36:08+00:00</t>
+    <t>2026-04-09T07:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
